--- a/projects/bridge-plan-maker.xlsx
+++ b/projects/bridge-plan-maker.xlsx
@@ -304,7 +304,7 @@
     <t xml:space="preserve">Doe </t>
   </si>
   <si>
-    <t xml:space="preserve">John</t>
+    <t xml:space="preserve">Jane</t>
   </si>
   <si>
     <t xml:space="preserve">KLHC</t>
@@ -2595,9 +2595,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="33" width="12.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="33" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="33" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="33" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="33" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="33" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="33" width="34"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="17" style="33" width="9.16"/>
   </cols>
   <sheetData>
@@ -3502,7 +3500,7 @@
     <row r="2" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="60" t="str">
         <f aca="false">VLOOKUP(E2,'Patient Information'!1:65535,2)&amp;", "&amp;VLOOKUP(E2,'Patient Information'!1:65535,3)</f>
-        <v>Doe , John</v>
+        <v>Doe , Jane</v>
       </c>
       <c r="B2" s="61"/>
       <c r="C2" s="61"/>
